--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D2">
-        <v>295</v>
+        <v>394</v>
       </c>
       <c r="E2">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>292</v>
+        <v>417</v>
       </c>
       <c r="E3">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
@@ -430,7 +430,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2">
         <v>394</v>
@@ -439,7 +439,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -453,13 +453,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>426</v>
